--- a/data/raw_lab_data/fe_analysis.xlsx
+++ b/data/raw_lab_data/fe_analysis.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/230e3d7962ef86ae/Kassel/prelim-lab-data/paul_lester/FuhrbergerColumns/data/exp_raw/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vcant\Documents\ffa_colexperiment\data\raw_lab_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{80C290CA-926E-E047-9F95-DA009F2A6262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60F540A3-AFA5-45BF-8A68-4EC1B6160E41}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C612C10-DB26-4A75-AB8D-648B939814CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C8071D3B-C586-244C-B46E-B25A50D33177}"/>
   </bookViews>
